--- a/knowledge/04_价格卡/询价清单.xlsx
+++ b/knowledge/04_价格卡/询价清单.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8400</v>
+        <v>7878</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -631,31 +631,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LD</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LDPE 新料（2426H 类）</t>
+          <t>HDPE 膜料（5000S 类）</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MFR 2.0，密度 0.922</t>
+          <t>MFR 0.9，密度 0.95</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2426H/2426K</t>
+          <t>5000S/HHMTR144</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>在包装膜中主要提供优良的光学性能（低雾度、高光泽）、良好的热封性能（低起封温度、高热封强度）和加工流动性。其长支链结构赋予熔体强度，利于吹膜膜泡稳定。常与LLDPE或HDPE共混，以平衡力学性能与光学/热封性能。</t>
+          <t>挺度；透明产品里拖后腿</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>9950</v>
+        <v>8400</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -665,207 +665,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>LL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HDPE 膜料（5000S 类）</t>
+          <t>C4 LLDPE（7042 类）</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MFR 0.9，密度 0.95</t>
+          <t>现用牌号</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5000S/HHMTR144</t>
+          <t>现用</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>挺度；透明产品里拖后腿</t>
+          <t>基准价格（含税到厂）</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>8400</v>
+        <v>12000</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>LL</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>C4 LLDPE（7042 类）</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>现用牌号</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>现用</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>基准价格（含税到厂）</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>12000</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>mLL8</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>茂金属 LLDPE（C8，Elite 类）</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>MFR 0.8～1.2，密度 0.916 左右，辛烯共聚</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Elite 5400 类</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>同上，高韧性版本</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>9900</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>MDPE 膜料</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>MDPE 吹膜级，密度 0.93～0.94</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>按供应商</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>挺度与成本折中</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>8700</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>LL6</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>C6 LLDPE（齐格勒己烯共聚）</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>MFR 1.0 左右，己烯共聚，吹膜级</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>按供应商</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>LLDPE 的低价升级</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>8900</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>mLL</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>茂金属 LLDPE（C6）</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>MFR 0.8～1.2，密度 0.916～0.920，己烯共聚，吹膜级</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>国产茂金属 / 1018、2045 类</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>少量替代 LLDPE，提高韧性</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>9400</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/knowledge/04_价格卡/询价清单.xlsx
+++ b/knowledge/04_价格卡/询价清单.xlsx
@@ -495,31 +495,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LLC</t>
+          <t>LL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>国产 C4 LLDPE（7042 类）</t>
+          <t>C4 LLDPE（7042 类）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C4 LLDPE 吹膜级，MFR 1.5～2.5，密度 0.916～0.920（含副牌/宽规格料报价）</t>
+          <t>现用牌号</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7042 / 218W / DFDA-7042</t>
+          <t>现用</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>直接替代现用 LLDPE</t>
+          <t>基准价格（含税到厂）</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>7878</v>
+        <v>12000</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -529,31 +529,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>LLC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>再生高压一级透明料</t>
+          <t>国产 C4 LLDPE（7042 类）</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MFR 2.0，密度 0.922</t>
+          <t>C4 LLDPE 吹膜级，MFR 1.5～2.5，密度 0.916～0.920（含副牌/宽规格料报价）</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7042 / 218W / DFDA-7042</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>现用；成本主力</t>
+          <t>直接替代现用 LLDPE</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8000</v>
+        <v>7878</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -563,31 +563,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>再生线性一级料（工业膜回料）</t>
+          <t>HDPE 膜料（5000S 类）</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>工业膜/边角料来源，无 PIB，MFR 1～3，灰分 ≤ 0.3%</t>
+          <t>MFR 0.9，密度 0.95</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5000S/HHMTR144</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>补充韧性的再生料</t>
+          <t>挺度；透明产品里拖后腿</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5900</v>
+        <v>8400</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -597,31 +597,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AD</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>功能助剂母料（PPA + 抗氧）</t>
+          <t>再生高压一级透明料</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PPA + 抗氧复合，LLDPE 载体</t>
+          <t>MFR 2.0，密度 0.922</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>按供应商</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>加工助剂</t>
+          <t>现用；成本主力</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>12500</v>
+        <v>8000</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -631,31 +631,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HDPE 膜料（5000S 类）</t>
+          <t>再生线性一级料（工业膜回料）</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MFR 0.9，密度 0.95</t>
+          <t>工业膜/边角料来源，无 PIB，MFR 1～3，灰分 ≤ 0.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5000S/HHMTR144</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>挺度；透明产品里拖后腿</t>
+          <t>补充韧性的再生料</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>8400</v>
+        <v>5900</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -665,31 +665,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LL</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>C4 LLDPE（7042 类）</t>
+          <t>功能助剂母料（PPA + 抗氧）</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>现用牌号</t>
+          <t>PPA + 抗氧复合，LLDPE 载体</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>现用</t>
+          <t>按供应商</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>基准价格（含税到厂）</t>
+          <t>加工助剂</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
